--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -564,7 +564,7 @@
         <v>2026-03-02T13:32:57.681Z</v>
       </c>
       <c r="G6">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="H6" t="str">
         <v/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -555,7 +555,7 @@
         <v>22028aim30@gmail.com</v>
       </c>
       <c r="D6" t="str">
-        <v>$2b$10$xwZbjFmfLYInQpO8FFN0XeWJ4QofYTEJg39p8WHR4NL.0cxWh8Rlm</v>
+        <v>$2b$10$RnUKjH/mRBpHlwJHbowLLuWpCVcP.GqsSObAbE9m7/dudA0Mb90Aa</v>
       </c>
       <c r="E6" t="str">
         <v>user</v>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,6 +427,12 @@
       <c r="I1" t="str">
         <v>Custom Title</v>
       </c>
+      <c r="J1" t="str">
+        <v>Reset Code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Reset Expiry</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -564,18 +570,24 @@
         <v>2026-03-02T13:32:57.681Z</v>
       </c>
       <c r="G6">
-        <v>100000</v>
+        <v>99900</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
         <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>529867</v>
+      </c>
+      <c r="K6" t="str">
+        <v>1772554179841</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>